--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:46</t>
+    <t xml:space="preserve">2026-09-09 22:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:33</t>
+    <t xml:space="preserve">2026-09-12 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:50</t>
+    <t xml:space="preserve">2026-09-24 00:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:28</t>
+    <t xml:space="preserve">2026-09-27 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17.07</v>
+        <v>170.68</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9.76</v>
+        <v>97.55</v>
       </c>
     </row>
     <row r="4">
@@ -578,7 +578,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.59</v>
+        <v>95.87</v>
       </c>
     </row>
     <row r="5">
@@ -595,7 +595,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8.7</v>
+        <v>86.95</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7.87</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7.56</v>
+        <v>75.6</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.95</v>
+        <v>69.48</v>
       </c>
     </row>
     <row r="9">
@@ -663,7 +663,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6.53</v>
+        <v>65.27</v>
       </c>
     </row>
     <row r="10">
@@ -680,7 +680,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6.46</v>
+        <v>64.6</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6.17</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="12">
@@ -714,7 +714,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.56</v>
+        <v>55.62</v>
       </c>
     </row>
     <row r="13">
@@ -731,7 +731,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5.15</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="14">
@@ -748,7 +748,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4.3</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.29</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="16">
@@ -782,7 +782,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3.99</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="17">
@@ -799,7 +799,7 @@
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3.29</v>
+        <v>32.91</v>
       </c>
     </row>
     <row r="18">
@@ -816,7 +816,7 @@
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.68</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="19">
@@ -833,7 +833,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2.54</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="20">
@@ -850,7 +850,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2.4</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="21">
@@ -867,7 +867,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.47</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="22">
@@ -884,7 +884,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-4.13</v>
+        <v>-41.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:10</t>
+    <t xml:space="preserve">2026-10-01 20:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:57</t>
+    <t xml:space="preserve">2026-10-02 13:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Pemuco</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">San Ignacio</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:33</t>
+    <t xml:space="preserve">2026-10-04 08:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:14</t>
+    <t xml:space="preserve">2026-10-05 08:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
